--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -411,7 +411,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -443,7 +443,7 @@
 #1 
 5s左右, 开头无BGM，
 0：00 - 0：08 音乐淡入,玩家使用电脑播放BGM
-0：08 音乐淡出，玩家杀死AI，音乐停止。玩家拾取地上钥匙卡。
+0：08 音乐淡出，玩家杀死AI，音乐停止。玩家拾取地上钥匙卡。LOGO出现
 #2 
 3s左右，玩家走向通往大厅的门。
 0：08 - 0：11 音乐淡入，玩家缓慢进入大厅，随着画面逐渐亮。
@@ -462,7 +462,7 @@
 1：50 - 1：54 音乐淡入，玩家从售货机走向门
 1：54 - 1：57(break your fucking face) ，玩家打开门，放置Abel，躲在门后，Abel爆炸（卡1：57）
 #6
-混剪10s直到预告结束[选用片段摘自1：57 - 2：27(so come and get it) ]</t>
+混剪10s直到预告结束[选用片段摘自1：57 - 2：27(so come and get it) ]，LOGO出现</t>
   </si>
   <si>
     <t>宣传片总时长
@@ -475,6 +475,15 @@
 总时长：87s</t>
   </si>
   <si>
+    <t>引擎内工作优先级排序
+修改扫描，让扫描只播放一次
+子弹Mesh，射击粒子特效
+笔记本亮屏画面，笔记本铃声
+敌人死后钥匙卡生成
+Abel AI配音
+掉落发出响声和掉落杀死AI的物体Mesh</t>
+  </si>
+  <si>
     <t>章节</t>
   </si>
   <si>
@@ -536,7 +545,8 @@
     <t>笔记本铃声，AI逐渐靠近的脚步声</t>
   </si>
   <si>
-    <t>玩家出现，AI被暗杀倒地，身上钥匙卡掉落</t>
+    <t>玩家出现，AI被暗杀倒地，身上钥匙卡掉落
+显示游戏LOGO</t>
   </si>
   <si>
     <t>0：08 音乐淡出，玩家杀死AI，玩家拾取地上钥匙卡</t>
@@ -698,6 +708,9 @@
   </si>
   <si>
     <t>场景实机</t>
+  </si>
+  <si>
+    <t>显示游戏LOGO</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1657,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="15" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1"/>
@@ -1659,7 +1672,7 @@
     <col min="10" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="408" customHeight="1" spans="1:4">
+    <row r="1" ht="408" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1671,281 +1684,284 @@
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3" ht="87.95" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="13.5"/>
     <row r="5" ht="106.15" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>=DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" spans="3:7">
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" ht="106.15" spans="3:6">
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="106.15" spans="3:7">
-      <c r="C9" s="1" t="s">
-        <v>23</v>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</f>
         <v>=DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:7">
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="106.15" spans="3:5">
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</f>
         <v>=DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="13.5"/>
     <row r="16" ht="106.15" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</f>
         <v>=DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="18" ht="13.5"/>
     <row r="19" ht="106.15" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="106.15" spans="2:6">
       <c r="B20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</f>
         <v>=DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" ht="106.15" spans="2:5">
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</f>
         <v>=DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" ht="106.15" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</f>
         <v>=DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" ht="106.15" spans="3:7">
       <c r="C25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="3:7">
       <c r="C26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="3:5">
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" s="3"/>
     </row>
     <row r="28" ht="26" customHeight="1" spans="3:7">
       <c r="C28" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E28" s="3"/>
       <c r="G28" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="3:5">
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E29" s="3"/>
     </row>
     <row r="30" ht="106.15" spans="3:5">
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
@@ -1955,71 +1971,76 @@
     </row>
     <row r="31" ht="106.15" spans="3:5">
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" ht="106.15" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="3:5">
       <c r="C34" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" ht="106.15" spans="3:5">
       <c r="C35" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="3:3">
       <c r="C39" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:3">
+      <c r="C40" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="21480" windowHeight="7950"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,7 +411,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -536,6 +536,9 @@
     <t>桌子</t>
   </si>
   <si>
+    <t>2. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
     <t xml:space="preserve">画面聚焦与笔记本上，AI虚焦
 音乐吸引AI前来检查，AI从画面左上角逐渐走进查看
 AI在靠近后只显露出下半身
@@ -545,6 +548,9 @@
     <t>笔记本铃声，AI逐渐靠近的脚步声</t>
   </si>
   <si>
+    <t>3. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
     <t>玩家出现，AI被暗杀倒地，身上钥匙卡掉落
 显示游戏LOGO</t>
   </si>
@@ -558,7 +564,7 @@
     <t>笔记本亮屏画面，笔记本铃声</t>
   </si>
   <si>
-    <t>2. 夜晚，熄灯的公司房间内</t>
+    <t>4. 夜晚，熄灯的公司房间内</t>
   </si>
   <si>
     <t>玩家捡起钥匙卡，镜头从笔记本前逐渐回归到玩家的第三人称镜头，摄像头移向通往大厅的门</t>
@@ -571,6 +577,9 @@
   </si>
   <si>
     <t>敌人死后钥匙卡生成</t>
+  </si>
+  <si>
+    <t>5. 夜晚，熄灯的公司房间内</t>
   </si>
   <si>
     <t>玩家在黑暗的公司中蹲伏前进，前往大厅（弗雷姆大厅）
@@ -604,7 +613,7 @@
     <t>子弹Mesh，射击粒子特效</t>
   </si>
   <si>
-    <t>视角切向黑暗中的机器人，机器人一台接着一台逐个从静止状态进入警戒状态，并开始移动</t>
+    <t>在警报声中，视角切向黑暗中的机器人，机器人一台接着一台逐个从静止状态进入警戒状态，并开始移动</t>
   </si>
   <si>
     <t>0：21 - 0：25 摄像头切到在全黑的公司某处内，大批机器人听到枪声，进入警戒状态，向摄像头移动</t>
@@ -632,6 +641,9 @@
   </si>
   <si>
     <t>画面倒放（倒带）的音效</t>
+  </si>
+  <si>
+    <t>2. 夜晚，明亮的大厅内</t>
   </si>
   <si>
     <t>Abel告诉玩家，放下枪，不要惊动守卫，不能够冲动，要利用Abel的技能一步步潜入进去</t>
@@ -654,16 +666,28 @@
     <t>修改扫描，让扫描只播放一次</t>
   </si>
   <si>
+    <t>4. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
     <t>玩家使用全息投影，引诱开敌人，然后从他身后蹲伏通过</t>
   </si>
   <si>
+    <t>5. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
     <t>玩家对天花板去物质化，天花板上面的物体掉下来砸死AI</t>
   </si>
   <si>
     <t>掉落发出响声和掉落杀死AI的物体Mesh</t>
   </si>
   <si>
+    <t>6. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
     <t>玩家读取敌人内心，获得密码，使用密码在密码锁上开门</t>
+  </si>
+  <si>
+    <t>7. 夜晚，明亮的大厅内</t>
   </si>
   <si>
     <t>玩家在一个门口放置重生点</t>
@@ -1689,7 +1713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2" ht="13.5"/>
     <row r="3" ht="87.95" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>5</v>
@@ -1754,214 +1778,241 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="106.15" spans="3:6">
+    <row r="8" ht="106.15" spans="2:6">
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="106.15" spans="3:7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="106.15" spans="2:7">
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</f>
         <v>=DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:7">
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" ht="106.15" spans="3:5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="106.15" spans="2:5">
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</f>
         <v>=DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" ht="13.5"/>
     <row r="16" ht="106.15" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</f>
         <v>=DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="18" ht="13.5"/>
     <row r="19" ht="106.15" spans="1:7">
       <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="106.15" spans="2:6">
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</f>
         <v>=DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" ht="106.15" spans="2:5">
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</f>
         <v>=DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" ht="106.15" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</f>
         <v>=DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" ht="106.15" spans="3:7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" ht="106.15" spans="2:7">
+      <c r="B25" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="3:7">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="2:7">
+      <c r="B26" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C26" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="3:5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="2:5">
+      <c r="B27" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" ht="26" customHeight="1" spans="3:7">
+    <row r="28" ht="26" customHeight="1" spans="2:7">
+      <c r="B28" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E28" s="3"/>
       <c r="G28" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="3:5">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:5">
+      <c r="B29" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" ht="106.15" spans="3:5">
+    <row r="30" ht="106.15" spans="2:5">
+      <c r="B30" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
@@ -1971,76 +2022,82 @@
     </row>
     <row r="31" ht="106.15" spans="3:5">
       <c r="C31" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D31" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" ht="106.15" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1" spans="3:5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="2:5">
+      <c r="B34" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C34" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" ht="106.15" spans="3:5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" ht="106.15" spans="2:5">
+      <c r="B35" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="3:3">
       <c r="C39" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:3">
       <c r="C40" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -411,7 +411,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -503,6 +503,9 @@
   </si>
   <si>
     <t>新增工作量</t>
+  </si>
+  <si>
+    <t>除BGM外文件</t>
   </si>
   <si>
     <t>章节一</t>
@@ -1681,8 +1684,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="15" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="15" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1"/>
     <col min="2" max="2" width="67.125" style="1" customWidth="1"/>
@@ -1713,8 +1716,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="13.5"/>
-    <row r="3" ht="87.95" customHeight="1" spans="1:7">
+    <row r="2"/>
+    <row r="3" ht="87.95" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1735,284 +1738,287 @@
       </c>
       <c r="G3" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="13.5"/>
     <row r="5" ht="106.15" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>=DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="3:7">
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="106.15" spans="2:6">
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="106.15" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</f>
         <v>=DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:7">
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" ht="106.15" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</f>
         <v>=DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="13.5"/>
     <row r="16" ht="106.15" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</f>
         <v>=DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="18" ht="13.5"/>
     <row r="19" ht="106.15" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" ht="106.15" spans="2:6">
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</f>
         <v>=DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="106.15" spans="2:5">
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</f>
         <v>=DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" ht="106.15" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</f>
         <v>=DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" ht="106.15" spans="2:7">
       <c r="B25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="2:7">
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="2:5">
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3"/>
     </row>
     <row r="28" ht="26" customHeight="1" spans="2:7">
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="3"/>
       <c r="G28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:5">
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E29" s="3"/>
     </row>
     <row r="30" ht="106.15" spans="2:5">
       <c r="B30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
@@ -2022,82 +2028,82 @@
     </row>
     <row r="31" ht="106.15" spans="3:5">
       <c r="C31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" ht="106.15" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="2:5">
       <c r="B34" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" ht="106.15" spans="2:5">
       <c r="B35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="3:3">
       <c r="C39" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:3">
       <c r="C40" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21480" windowHeight="7950"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,7 +411,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="91">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -505,7 +505,7 @@
     <t>新增工作量</t>
   </si>
   <si>
-    <t>除BGM外文件</t>
+    <t>完成状况</t>
   </si>
   <si>
     <t>章节一</t>
@@ -524,6 +524,9 @@
     <t>微弱的机器人巡逻脚步声</t>
   </si>
   <si>
+    <t>完成：T1-1</t>
+  </si>
+  <si>
     <t>画面逐渐对焦到笔记本上</t>
   </si>
   <si>
@@ -537,6 +540,9 @@
   </si>
   <si>
     <t>桌子</t>
+  </si>
+  <si>
+    <t>待补充：笔记本播放音乐</t>
   </si>
   <si>
     <t>2. 夜晚，熄灯的公司房间内</t>
@@ -554,7 +560,7 @@
     <t>3. 夜晚，熄灯的公司房间内</t>
   </si>
   <si>
-    <t>玩家出现，AI被暗杀倒地，身上钥匙卡掉落
+    <t>玩家出现，AI被暗杀倒地
 显示游戏LOGO</t>
   </si>
   <si>
@@ -567,10 +573,13 @@
     <t>笔记本亮屏画面，笔记本铃声</t>
   </si>
   <si>
+    <t>待补充：显示游戏LOGO</t>
+  </si>
+  <si>
     <t>4. 夜晚，熄灯的公司房间内</t>
   </si>
   <si>
-    <t>玩家捡起钥匙卡，镜头从笔记本前逐渐回归到玩家的第三人称镜头，摄像头移向通往大厅的门</t>
+    <t>镜头从笔记本前逐渐回归到玩家的第三人称镜头，摄像头移向通往大厅的门</t>
   </si>
   <si>
     <t>3s左右，无BGM</t>
@@ -623,6 +632,9 @@
   </si>
   <si>
     <t>机器人进入警戒音效</t>
+  </si>
+  <si>
+    <t>完成：T3-2</t>
   </si>
   <si>
     <t>3. 夜晚，明亮的大厅内</t>
@@ -693,7 +705,7 @@
     <t>7. 夜晚，明亮的大厅内</t>
   </si>
   <si>
-    <t>玩家在一个门口放置重生点</t>
+    <t>玩家打碎门口摄像头，玩家在一个门口放置重生点</t>
   </si>
   <si>
     <t>玩家开门，进入房间，被四面八方的敌人射死</t>
@@ -1104,12 +1116,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1236,7 +1263,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1248,34 +1275,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1360,7 +1387,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1371,6 +1398,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1694,7 +1727,7 @@
     <col min="5" max="5" width="72.0583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="43.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="36.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="1"/>
+    <col min="8" max="8" width="24.1083333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="27.5" style="1" customWidth="1"/>
     <col min="10" max="16384" width="15.625" style="1"/>
   </cols>
@@ -1716,395 +1749,506 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2" ht="13.5"/>
     <row r="3" ht="87.95" customHeight="1" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="13.5"/>
-    <row r="5" ht="106.15" spans="1:6">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="106.15" spans="1:8">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="str">
+      <c r="D5" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>=DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" ht="13.5" spans="3:3">
-      <c r="C6" s="1" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="13.5" spans="3:7">
-      <c r="C7" s="1" t="s">
+    <row r="6" ht="13.5" spans="1:8">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" ht="106.15" spans="2:6">
-      <c r="B8" s="1" t="s">
+      <c r="G7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1" t="str">
+    </row>
+    <row r="8" ht="106.15" spans="1:8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="106.15" spans="2:7">
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="1" t="str">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="106.15" spans="1:8">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</f>
         <v>=DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="E9" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:7">
-      <c r="B11" s="1" t="s">
+      <c r="F9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="G9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="H9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="1" t="s">
+    </row>
+    <row r="10" ht="13.5" spans="1:8">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" ht="106.15" spans="2:5">
-      <c r="B12" s="1" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="1" t="str">
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" ht="106.15" spans="1:8">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</f>
         <v>=DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" ht="13.5"/>
-    <row r="16" ht="106.15" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="1" t="str">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="16" ht="106.15" spans="1:8">
+      <c r="A16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</f>
         <v>=DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="3"/>
+      <c r="E16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="18" ht="13.5"/>
-    <row r="19" ht="106.15" spans="1:7">
-      <c r="A19" s="1" t="s">
+    <row r="19" ht="106.15" spans="1:8">
+      <c r="A19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="1" t="str">
+      <c r="C19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" ht="106.15" spans="2:6">
-      <c r="B20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="1" t="str">
+      <c r="E19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" ht="106.15" spans="1:8">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</f>
         <v>=DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" ht="106.15" spans="2:5">
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="E20" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="1" t="str">
+      <c r="F20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" ht="106.15" spans="1:8">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</f>
         <v>=DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" ht="106.15" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="1" t="str">
+      <c r="E21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="24" ht="106.15" spans="1:8">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</f>
         <v>=DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" ht="106.15" spans="2:7">
-      <c r="B25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="1" t="str">
+      <c r="E24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" ht="106.15" spans="1:8">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="2:7">
-      <c r="B26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="E25" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="2:5">
-      <c r="B27" s="1" t="s">
+      <c r="F25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="G25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:8">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" ht="26" customHeight="1" spans="2:7">
-      <c r="B28" s="1" t="s">
+      <c r="D26" s="4"/>
+      <c r="E26" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="3"/>
-      <c r="G28" s="1" t="s">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:8">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:5">
-      <c r="B29" s="1" t="s">
+      <c r="C27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" ht="26" customHeight="1" spans="1:8">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" ht="106.15" spans="2:5">
-      <c r="B30" s="1" t="s">
+      <c r="C28" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:8">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" ht="106.15" spans="1:8">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
         <v>=DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</v>
       </c>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" ht="106.15" spans="3:5">
-      <c r="C31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="1" t="str">
+      <c r="E30" s="5"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" ht="106.15" spans="1:8">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" ht="106.15" spans="1:5">
-      <c r="A33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" s="1" t="str">
+      <c r="E31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="33" ht="106.15" spans="1:8">
+      <c r="A33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1" spans="2:5">
-      <c r="B34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="35" ht="106.15" spans="2:5">
-      <c r="B35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="1" t="str">
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:8">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" ht="106.15" spans="1:8">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="4" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:5">
-      <c r="A38" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="E35" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="3:3">
-      <c r="C39" s="1" t="s">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:8">
+      <c r="A38" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:3">
-      <c r="C40" s="1" t="s">
+      <c r="B38" s="4" t="s">
         <v>86</v>
       </c>
+      <c r="C38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:8">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:8">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D38E4F6-3A7A-4550-93DF-74D069660060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADA4E6E-79EE-49CC-A6C0-E914A1318FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29655" yWindow="2205" windowWidth="21585" windowHeight="8835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32025" yWindow="4095" windowWidth="21585" windowHeight="8835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Excel分镜" sheetId="1" r:id="rId1"/>
+    <sheet name="Abel语音" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="119">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -430,6 +430,284 @@
 游玩实机、技能释放的混剪
 最终再次以炸弹爆炸收尾，在爆炸中，Abel跳舞挑衅士兵，摄像头推进到蓝色爆炸与Abel
 出现游戏LOGO，预告结束</t>
+  </si>
+  <si>
+    <t>章节</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>概念图</t>
+  </si>
+  <si>
+    <t>音乐</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>新增工作量</t>
+  </si>
+  <si>
+    <t>完成状况</t>
+  </si>
+  <si>
+    <t>章节一</t>
+  </si>
+  <si>
+    <t>1. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
+    <t>画面聚焦于笔记本后的环境上，笔记本虚焦
+笔记本电脑黑屏</t>
+  </si>
+  <si>
+    <t>5s左右, 开头无BGM，</t>
+  </si>
+  <si>
+    <t>微弱的机器人巡逻脚步声</t>
+  </si>
+  <si>
+    <t>完成：T1-1</t>
+  </si>
+  <si>
+    <t>画面逐渐对焦到笔记本上</t>
+  </si>
+  <si>
+    <t>笔记本屏幕被点亮，玩家使用笔记本播放音乐</t>
+  </si>
+  <si>
+    <t>0：00 - 0：08 音乐淡入,玩家使用电脑播放BGM</t>
+  </si>
+  <si>
+    <t>笔记本铃声</t>
+  </si>
+  <si>
+    <t>桌子</t>
+  </si>
+  <si>
+    <t>待补充：笔记本播放音乐</t>
+  </si>
+  <si>
+    <t>2. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面聚焦与笔记本上，AI虚焦
+音乐吸引AI前来检查，AI从画面左上角逐渐走进查看
+AI在靠近后只显露出下半身
+</t>
+  </si>
+  <si>
+    <t>笔记本铃声，AI逐渐靠近的脚步声</t>
+  </si>
+  <si>
+    <t>3. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
+    <t>玩家出现，AI被暗杀倒地
+显示游戏LOGO</t>
+  </si>
+  <si>
+    <t>0：08 音乐淡出，玩家杀死AI，玩家拾取地上钥匙卡</t>
+  </si>
+  <si>
+    <t>笔记本铃声，轻微的敌人倒地声，卡片掉落声</t>
+  </si>
+  <si>
+    <t>笔记本亮屏画面，笔记本铃声</t>
+  </si>
+  <si>
+    <t>待补充：显示游戏LOGO</t>
+  </si>
+  <si>
+    <t>4. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
+    <t>镜头从笔记本前逐渐回归到玩家的第三人称镜头，摄像头移向通往大厅的门</t>
+  </si>
+  <si>
+    <t>3s左右，无BGM</t>
+  </si>
+  <si>
+    <t>玩家拾取声音</t>
+  </si>
+  <si>
+    <t>敌人死后钥匙卡生成</t>
+  </si>
+  <si>
+    <t>5. 夜晚，熄灯的公司房间内</t>
+  </si>
+  <si>
+    <t>玩家在黑暗的公司中蹲伏前进，前往大厅（弗雷姆大厅）
+大厅灯亮，但玩家所处的房屋全黑，随着玩家往前移动画面亮度逐渐提高</t>
+  </si>
+  <si>
+    <t>0：08 - 0：11 音乐淡入，玩家缓慢进入大厅，随着画面逐渐变亮</t>
+  </si>
+  <si>
+    <t>章节二</t>
+  </si>
+  <si>
+    <t>1. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>玩家抵达大厅，慢移第三人称摄像机，环绕观看整个楼内（AI，场景等）</t>
+  </si>
+  <si>
+    <t>0：11 - 0：14 镜头以玩家视角环顾三楼</t>
+  </si>
+  <si>
+    <t>章节三</t>
+  </si>
+  <si>
+    <t>玩家举起枪，瞄准其中一名巡逻士兵</t>
+  </si>
+  <si>
+    <t>0：14 - 0：21 玩家举枪瞄准AI，向AI开火，开火瞬间，摄像头从玩家的第三人称摄像头逐渐靠向子弹并最终聚焦于子弹上，画面变黑</t>
+  </si>
+  <si>
+    <t>子弹Mesh，射击粒子特效</t>
+  </si>
+  <si>
+    <t>在警报声中，视角切向黑暗中的机器人，机器人一台接着一台逐个从静止状态进入警戒状态，并开始移动</t>
+  </si>
+  <si>
+    <t>0：21 - 0：25 摄像头切到在全黑的公司某处内，大批机器人听到枪声，进入警戒状态，向摄像头移动</t>
+  </si>
+  <si>
+    <t>机器人进入警戒音效</t>
+  </si>
+  <si>
+    <t>完成：T3-2</t>
+  </si>
+  <si>
+    <t>3. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>四面八方士兵涌来，玩家死亡，显示UI Mission fail</t>
+  </si>
+  <si>
+    <t>0：25 - 0：30 音乐淡出，玩家受到攻击，死亡，Mission Fail。</t>
+  </si>
+  <si>
+    <t>章节四</t>
+  </si>
+  <si>
+    <t>前一章的内容快速倒放，并且加上蓝色后期效果，表示这是Abel推测的结果</t>
+  </si>
+  <si>
+    <t>2s左右，画面倒放，无BGM</t>
+  </si>
+  <si>
+    <t>画面倒放（倒带）的音效</t>
+  </si>
+  <si>
+    <t>2. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>Abel告诉玩家，放下枪，不要惊动守卫，不能够冲动，要利用Abel的技能一步步潜入进去</t>
+  </si>
+  <si>
+    <t>3s左右，Abel语音提示，无BGM；</t>
+  </si>
+  <si>
+    <t>Abel的配音</t>
+  </si>
+  <si>
+    <t>玩家使用扫描，探查出楼内的AI</t>
+  </si>
+  <si>
+    <t>1：14 - 1：31(They wanna stop us)
+玩家进入骇客模式并且使用扫描的瞬间，BGM立刻开始
+玩家放置完重生点后，BGM淡出</t>
+  </si>
+  <si>
+    <t>修改扫描，让扫描只播放一次</t>
+  </si>
+  <si>
+    <t>4. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>玩家使用全息投影，引诱开敌人，然后从他身后蹲伏通过</t>
+  </si>
+  <si>
+    <t>5. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>玩家对天花板去物质化，天花板上面的物体掉下来砸死AI</t>
+  </si>
+  <si>
+    <t>掉落发出响声和掉落杀死AI的物体Mesh</t>
+  </si>
+  <si>
+    <t>6. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>玩家读取敌人内心，获得密码，使用密码在密码锁上开门</t>
+  </si>
+  <si>
+    <t>7. 夜晚，明亮的大厅内</t>
+  </si>
+  <si>
+    <t>玩家打碎门口摄像头，玩家在一个门口放置重生点</t>
+  </si>
+  <si>
+    <t>玩家开门，进入房间，被四面八方的敌人射死</t>
+  </si>
+  <si>
+    <t>5s左右，无BGM</t>
+  </si>
+  <si>
+    <t>章节五</t>
+  </si>
+  <si>
+    <t>玩家在门口重生点重生，看到门口的售货机，购买神秘武器。</t>
+  </si>
+  <si>
+    <t>玩家走向门，随着离门越来越近，BGM声音越来越大</t>
+  </si>
+  <si>
+    <t>1：50 - 1：54 音乐淡入</t>
+  </si>
+  <si>
+    <t>玩家打开门，放置全息，敌人向全息移动，敌人被全息炸死</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1：54 - 1：57(break your fucking face) ，玩家打开门，放置Abel，躲在门后，Abel爆炸（卡1：57）
+</t>
+  </si>
+  <si>
+    <t>章节六</t>
+  </si>
+  <si>
+    <t>1. 任意</t>
+  </si>
+  <si>
+    <t>游玩实机（四个技能，射击，暗杀，攀爬）</t>
+  </si>
+  <si>
+    <t>1：57 - 2：27(so come and get it) 混剪直到预告结束
+混剪总共10s</t>
+  </si>
+  <si>
+    <t>场景实机</t>
+  </si>
+  <si>
+    <t>显示游戏LOGO</t>
+  </si>
+  <si>
+    <t>引擎内工作优先级排序
+修改扫描，让扫描只播放一次
+子弹Mesh，射击粒子特效
+笔记本亮屏画面，笔记本铃声
+敌人死后钥匙卡生成
+Abel AI配音
+掉落发出响声和掉落杀死AI的物体Mesh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>BGM选用：Break Stuff.Explicit.-Limp Bizkit
@@ -456,6 +734,7 @@
 1：54 - 1：57(break your fucking face) ，玩家打开门，放置Abel，躲在门后，Abel爆炸（卡1：57）
 #6
 混剪10s直到预告结束[选用片段摘自1：57 - 2：27(so come and get it) ]，LOGO出现</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>宣传片总时长
@@ -466,283 +745,114 @@
 #5 5s + 7s
 #6 10s
 总时长：87s</t>
-  </si>
-  <si>
-    <t>章节</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>概念图</t>
-  </si>
-  <si>
-    <t>音乐</t>
-  </si>
-  <si>
-    <t>音效</t>
-  </si>
-  <si>
-    <t>新增工作量</t>
-  </si>
-  <si>
-    <t>完成状况</t>
-  </si>
-  <si>
-    <t>章节一</t>
-  </si>
-  <si>
-    <t>1. 夜晚，熄灯的公司房间内</t>
-  </si>
-  <si>
-    <t>画面聚焦于笔记本后的环境上，笔记本虚焦
-笔记本电脑黑屏</t>
-  </si>
-  <si>
-    <t>5s左右, 开头无BGM，</t>
-  </si>
-  <si>
-    <t>微弱的机器人巡逻脚步声</t>
-  </si>
-  <si>
-    <t>完成：T1-1</t>
-  </si>
-  <si>
-    <t>画面逐渐对焦到笔记本上</t>
-  </si>
-  <si>
-    <t>笔记本屏幕被点亮，玩家使用笔记本播放音乐</t>
-  </si>
-  <si>
-    <t>0：00 - 0：08 音乐淡入,玩家使用电脑播放BGM</t>
-  </si>
-  <si>
-    <t>笔记本铃声</t>
-  </si>
-  <si>
-    <t>桌子</t>
-  </si>
-  <si>
-    <t>待补充：笔记本播放音乐</t>
-  </si>
-  <si>
-    <t>2. 夜晚，熄灯的公司房间内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">画面聚焦与笔记本上，AI虚焦
-音乐吸引AI前来检查，AI从画面左上角逐渐走进查看
-AI在靠近后只显露出下半身
-</t>
-  </si>
-  <si>
-    <t>笔记本铃声，AI逐渐靠近的脚步声</t>
-  </si>
-  <si>
-    <t>3. 夜晚，熄灯的公司房间内</t>
-  </si>
-  <si>
-    <t>玩家出现，AI被暗杀倒地
-显示游戏LOGO</t>
-  </si>
-  <si>
-    <t>0：08 音乐淡出，玩家杀死AI，玩家拾取地上钥匙卡</t>
-  </si>
-  <si>
-    <t>笔记本铃声，轻微的敌人倒地声，卡片掉落声</t>
-  </si>
-  <si>
-    <t>笔记本亮屏画面，笔记本铃声</t>
-  </si>
-  <si>
-    <t>待补充：显示游戏LOGO</t>
-  </si>
-  <si>
-    <t>4. 夜晚，熄灯的公司房间内</t>
-  </si>
-  <si>
-    <t>镜头从笔记本前逐渐回归到玩家的第三人称镜头，摄像头移向通往大厅的门</t>
-  </si>
-  <si>
-    <t>3s左右，无BGM</t>
-  </si>
-  <si>
-    <t>玩家拾取声音</t>
-  </si>
-  <si>
-    <t>敌人死后钥匙卡生成</t>
-  </si>
-  <si>
-    <t>5. 夜晚，熄灯的公司房间内</t>
-  </si>
-  <si>
-    <t>玩家在黑暗的公司中蹲伏前进，前往大厅（弗雷姆大厅）
-大厅灯亮，但玩家所处的房屋全黑，随着玩家往前移动画面亮度逐渐提高</t>
-  </si>
-  <si>
-    <t>0：08 - 0：11 音乐淡入，玩家缓慢进入大厅，随着画面逐渐变亮</t>
-  </si>
-  <si>
-    <t>章节二</t>
-  </si>
-  <si>
-    <t>1. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>玩家抵达大厅，慢移第三人称摄像机，环绕观看整个楼内（AI，场景等）</t>
-  </si>
-  <si>
-    <t>0：11 - 0：14 镜头以玩家视角环顾三楼</t>
-  </si>
-  <si>
-    <t>章节三</t>
-  </si>
-  <si>
-    <t>玩家举起枪，瞄准其中一名巡逻士兵</t>
-  </si>
-  <si>
-    <t>0：14 - 0：21 玩家举枪瞄准AI，向AI开火，开火瞬间，摄像头从玩家的第三人称摄像头逐渐靠向子弹并最终聚焦于子弹上，画面变黑</t>
-  </si>
-  <si>
-    <t>子弹Mesh，射击粒子特效</t>
-  </si>
-  <si>
-    <t>在警报声中，视角切向黑暗中的机器人，机器人一台接着一台逐个从静止状态进入警戒状态，并开始移动</t>
-  </si>
-  <si>
-    <t>0：21 - 0：25 摄像头切到在全黑的公司某处内，大批机器人听到枪声，进入警戒状态，向摄像头移动</t>
-  </si>
-  <si>
-    <t>机器人进入警戒音效</t>
-  </si>
-  <si>
-    <t>完成：T3-2</t>
-  </si>
-  <si>
-    <t>3. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>四面八方士兵涌来，玩家死亡，显示UI Mission fail</t>
-  </si>
-  <si>
-    <t>0：25 - 0：30 音乐淡出，玩家受到攻击，死亡，Mission Fail。</t>
-  </si>
-  <si>
-    <t>章节四</t>
-  </si>
-  <si>
-    <t>前一章的内容快速倒放，并且加上蓝色后期效果，表示这是Abel推测的结果</t>
-  </si>
-  <si>
-    <t>2s左右，画面倒放，无BGM</t>
-  </si>
-  <si>
-    <t>画面倒放（倒带）的音效</t>
-  </si>
-  <si>
-    <t>2. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>Abel告诉玩家，放下枪，不要惊动守卫，不能够冲动，要利用Abel的技能一步步潜入进去</t>
-  </si>
-  <si>
-    <t>3s左右，Abel语音提示，无BGM；</t>
-  </si>
-  <si>
-    <t>Abel的配音</t>
-  </si>
-  <si>
-    <t>玩家使用扫描，探查出楼内的AI</t>
-  </si>
-  <si>
-    <t>1：14 - 1：31(They wanna stop us)
-玩家进入骇客模式并且使用扫描的瞬间，BGM立刻开始
-玩家放置完重生点后，BGM淡出</t>
-  </si>
-  <si>
-    <t>修改扫描，让扫描只播放一次</t>
-  </si>
-  <si>
-    <t>4. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>玩家使用全息投影，引诱开敌人，然后从他身后蹲伏通过</t>
-  </si>
-  <si>
-    <t>5. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>玩家对天花板去物质化，天花板上面的物体掉下来砸死AI</t>
-  </si>
-  <si>
-    <t>掉落发出响声和掉落杀死AI的物体Mesh</t>
-  </si>
-  <si>
-    <t>6. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>玩家读取敌人内心，获得密码，使用密码在密码锁上开门</t>
-  </si>
-  <si>
-    <t>7. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>玩家打碎门口摄像头，玩家在一个门口放置重生点</t>
-  </si>
-  <si>
-    <t>玩家开门，进入房间，被四面八方的敌人射死</t>
-  </si>
-  <si>
-    <t>5s左右，无BGM</t>
-  </si>
-  <si>
-    <t>章节五</t>
-  </si>
-  <si>
-    <t>玩家在门口重生点重生，看到门口的售货机，购买神秘武器。</t>
-  </si>
-  <si>
-    <t>玩家走向门，随着离门越来越近，BGM声音越来越大</t>
-  </si>
-  <si>
-    <t>1：50 - 1：54 音乐淡入</t>
-  </si>
-  <si>
-    <t>玩家打开门，放置全息，敌人向全息移动，敌人被全息炸死</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1：54 - 1：57(break your fucking face) ，玩家打开门，放置Abel，躲在门后，Abel爆炸（卡1：57）
-</t>
-  </si>
-  <si>
-    <t>章节六</t>
-  </si>
-  <si>
-    <t>1. 任意</t>
-  </si>
-  <si>
-    <t>游玩实机（四个技能，射击，暗杀，攀爬）</t>
-  </si>
-  <si>
-    <t>1：57 - 2：27(so come and get it) 混剪直到预告结束
-混剪总共10s</t>
-  </si>
-  <si>
-    <t>场景实机</t>
-  </si>
-  <si>
-    <t>显示游戏LOGO</t>
-  </si>
-  <si>
-    <t>引擎内工作优先级排序
-修改扫描，让扫描只播放一次
-子弹Mesh，射击粒子特效
-笔记本亮屏画面，笔记本铃声
-敌人死后钥匙卡生成
-Abel AI配音
-掉落发出响声和掉落杀死AI的物体Mesh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T3-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T4-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T4-2~4-6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T4-7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T5-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T5-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣传片T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音Speech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT3-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT4-2~4-6</t>
+  </si>
+  <si>
+    <t>SpT4-7</t>
+  </si>
+  <si>
+    <t>SpT5-1</t>
+  </si>
+  <si>
+    <t>SpT5-2</t>
+  </si>
+  <si>
+    <t>SpT4-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音编号命名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintain combat focus. Do not compromise your position.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stop. Right now.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unless you want to die here.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your priority is eliminating the CEO. Nothing else matters.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the abilities I gave you. That's not a suggestion.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait—hostile signatures incoming!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lucky for you, I anticipated this. Next time? Eyes open.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try this approach instead. Make it count.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Don’t. Screw. This. Up.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://elevenlabs.io/app/speech-synthesis/text-to-speech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voice: Will</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -750,7 +860,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -775,6 +885,23 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -813,12 +940,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -834,18 +964,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1132,183 +1284,183 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="C1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>90</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:8" ht="87.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="D5" s="3" t="e">
         <f ca="1">_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>#NAME?</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>15</v>
+      <c r="E5" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="54" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</f>
         <v>=DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</f>
         <v>=DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -1318,20 +1470,20 @@
     <row r="13" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="D16" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</f>
         <v>=DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="3"/>
@@ -1340,64 +1492,64 @@
     <row r="18" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="19" spans="1:8" ht="27" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</f>
         <v>=DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D21" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</f>
         <v>=DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1405,23 +1557,23 @@
     </row>
     <row r="24" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</f>
         <v>=DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1429,54 +1581,54 @@
     <row r="25" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="6" t="s">
-        <v>65</v>
+      <c r="E26" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="6"/>
+      <c r="E27" s="7"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1484,29 +1636,29 @@
     <row r="28" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="6"/>
+      <c r="E28" s="7"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="6"/>
+      <c r="E29" s="7"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1514,16 +1666,16 @@
     <row r="30" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D30" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
         <v>=DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</v>
       </c>
-      <c r="E30" s="6"/>
+      <c r="E30" s="7"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1532,14 +1684,14 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D31" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1547,20 +1699,20 @@
     </row>
     <row r="33" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D33" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -1569,14 +1721,14 @@
     <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -1585,17 +1737,17 @@
     <row r="35" spans="1:8" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D35" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -1603,17 +1755,17 @@
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" s="3"/>
+      <c r="E38" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1623,10 +1775,10 @@
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="5"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1635,7 +1787,7 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1658,10 +1810,228 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="71.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="63.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="11"/>
+      <c r="B3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="11"/>
+      <c r="B4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="11"/>
+      <c r="B5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="11"/>
+      <c r="B6" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="11"/>
+      <c r="B7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="11"/>
+      <c r="B8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="11"/>
+      <c r="B9" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="11"/>
+      <c r="B10" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F1" r:id="rId1" xr:uid="{C7F4C5A3-60AB-4D08-8DE4-2B03BC8F3D92}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADA4E6E-79EE-49CC-A6C0-E914A1318FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9688CBD-D9E2-4CAA-8876-461B1EBECB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32025" yWindow="4095" windowWidth="21585" windowHeight="8835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel分镜" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="122">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -792,67 +792,105 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SpT4-2~4-6</t>
+    <t>SpT4-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音编号命名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintain combat focus. Do not compromise your position.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stop. Right now.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unless you want to die here.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your priority is eliminating the CEO. Nothing else matters.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the abilities I gave you. That's not a suggestion.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait—hostile signatures incoming!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lucky for you, I anticipated this. Next time? Eyes open.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try this approach instead. Make it count.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Don’t. Screw. This. Up.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ttsmaker.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Voice: 34号， Emotion 2402 - robert-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>🇬🇧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>united kingdom male voice</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT4-2(1)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT4-2(2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT4-2(3)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT5-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SpT4-7</t>
-  </si>
-  <si>
-    <t>SpT5-1</t>
-  </si>
-  <si>
-    <t>SpT5-2</t>
-  </si>
-  <si>
-    <t>SpT4-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>语音编号命名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maintain combat focus. Do not compromise your position.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stop. Right now.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unless you want to die here.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Your priority is eliminating the CEO. Nothing else matters.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use the abilities I gave you. That's not a suggestion.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wait—hostile signatures incoming!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lucky for you, I anticipated this. Next time? Eyes open.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Try this approach instead. Make it count.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Don’t. Screw. This. Up.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://elevenlabs.io/app/speech-synthesis/text-to-speech</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Voice: Will</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT5-1(1)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpT5-1(2)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -860,7 +898,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -907,6 +945,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -948,7 +992,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -967,12 +1011,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -988,11 +1026,14 @@
     <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1010,6 +1051,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4363062</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>152595</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A92CFC-9135-C5BF-EDDF-FDEDD3572B18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9496425" y="333375"/>
+          <a:ext cx="4382112" cy="1400370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1284,10 +1374,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -1336,7 +1426,7 @@
         <f ca="1">_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>#NAME?</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -1354,7 +1444,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1368,7 +1458,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1393,7 +1483,7 @@
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
@@ -1610,7 +1700,7 @@
         <v>62</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="13" t="s">
         <v>63</v>
       </c>
       <c r="F26" s="3"/>
@@ -1628,7 +1718,7 @@
         <v>66</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="13"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1642,7 +1732,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="7"/>
+      <c r="E28" s="13"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>69</v>
@@ -1658,7 +1748,7 @@
         <v>71</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1675,7 +1765,7 @@
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
         <v>=DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="13"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1764,7 +1854,7 @@
         <v>84</v>
       </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="13" t="s">
         <v>85</v>
       </c>
       <c r="F38" s="3"/>
@@ -1778,7 +1868,7 @@
         <v>86</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="6"/>
+      <c r="E39" s="12"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1820,212 +1910,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="9"/>
+      <c r="B3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="9"/>
+      <c r="B4" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="D4" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="9"/>
+      <c r="B5" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="9"/>
+      <c r="B6" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="C6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="9"/>
+      <c r="B7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="D7" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="9"/>
+      <c r="B8" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="9"/>
+      <c r="B9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="9"/>
+      <c r="B10" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="11"/>
-      <c r="B3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="11"/>
-      <c r="B4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="11"/>
-      <c r="B5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="11"/>
-      <c r="B6" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="11"/>
-      <c r="B7" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="11"/>
-      <c r="B10" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2034,6 +2124,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9688CBD-D9E2-4CAA-8876-461B1EBECB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A3D338-3164-4319-B004-9606341532AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="127">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -891,6 +891,26 @@
   </si>
   <si>
     <t>SpT5-1(2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保留第一张图片的主体结构和大致样式，并做出以下调整：1. 将主色调改为蓝色，类似于英特尔广告的颜色；2. 选择第二张图片中的一个图标，替换掉第一张图片中的图标；3.图中文字意思为共生体，可以做出额外的抽象图像设计来表达这一含义，尽量简洁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://app.layer.ai/medic1745665506/session/1caddb71-a24e-4a8e-930e-1cd521f993f2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abel Voice : John</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>安保头子Voice：Judas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女BOSS Voice: Lailah</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -992,7 +1012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1028,6 +1048,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1091,6 +1114,226 @@
         <a:xfrm>
           <a:off x="9496425" y="333375"/>
           <a:ext cx="4382112" cy="1400370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>122156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3783959</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>29907</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F368E0B-C0EA-07E6-5DAF-55F4BE892959}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9563100" y="2560556"/>
+          <a:ext cx="3736334" cy="1965151"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3762375</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>92380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DB19C8C-8EB5-9591-97FD-315A0DB8164D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13277850" y="2552700"/>
+          <a:ext cx="1714500" cy="2035480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2467167</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B170929-5D74-F385-E672-0399D6E8EE0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9525000" y="5524500"/>
+          <a:ext cx="2457642" cy="2362200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2124075</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3535816</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{752B01A1-8B10-8DA9-A7E9-513BA1ECEFBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11639550" y="8801100"/>
+          <a:ext cx="1411741" cy="4048125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2124373</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>105125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B44E091-39E7-FFD6-A212-4748D3037948}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9505950" y="8782050"/>
+          <a:ext cx="2133898" cy="2505425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1352,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1"/>
@@ -1426,7 +1669,7 @@
         <f ca="1">_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>#NAME?</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -1444,7 +1687,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="12"/>
+      <c r="E6" s="13"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1458,7 +1701,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1483,7 +1726,7 @@
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
@@ -1700,7 +1943,7 @@
         <v>62</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F26" s="3"/>
@@ -1718,7 +1961,7 @@
         <v>66</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="13"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1732,7 +1975,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="13"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
         <v>69</v>
@@ -1748,7 +1991,7 @@
         <v>71</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="13"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1765,7 +2008,7 @@
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
         <v>=DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</v>
       </c>
-      <c r="E30" s="13"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1854,7 +2097,7 @@
         <v>84</v>
       </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>85</v>
       </c>
       <c r="F38" s="3"/>
@@ -1868,7 +2111,7 @@
         <v>86</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="12"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1884,6 +2127,11 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="12" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1900,7 +2148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.25" customWidth="1"/>
@@ -2056,12 +2304,18 @@
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
+      <c r="F13" s="11" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
+      <c r="F14" s="7" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="9"/>
@@ -2075,56 +2329,67 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
     </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F32" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F51" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F1" r:id="rId1" xr:uid="{C7F4C5A3-60AB-4D08-8DE4-2B03BC8F3D92}"/>
+    <hyperlink ref="F13" r:id="rId2" xr:uid="{1D205812-9CFD-4D5E-8D01-420DD86489DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A3D338-3164-4319-B004-9606341532AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141A2220-11EA-4F63-980D-9BA014410543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel分镜" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -911,6 +911,54 @@
   </si>
   <si>
     <t>女BOSS Voice: Lailah</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐状况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡入1s，声音小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>声音小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI死亡音乐中断</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡入1s，玩家进入大厅音乐恢复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐淡出1s，玩家死亡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描完成，音乐立即开始</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家死亡，音乐停止</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐淡入2s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOGO出现，音乐停止</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -980,7 +1028,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1003,6 +1051,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1012,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1057,6 +1118,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1595,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1"/>
@@ -1610,7 +1677,7 @@
     <col min="10" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="408" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="408" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1627,8 +1694,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
-    <row r="3" spans="1:8" ht="87.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
+    <row r="3" spans="1:9" ht="87.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1650,12 +1717,17 @@
       <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="I3" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1676,11 +1748,14 @@
         <v>14</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I5" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
@@ -1690,11 +1765,14 @@
       <c r="E6" s="13"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I6" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
@@ -1710,11 +1788,14 @@
       <c r="G7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="54" x14ac:dyDescent="0.15">
+      <c r="I7" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>22</v>
@@ -1731,11 +1812,14 @@
         <v>24</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="I8" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>25</v>
@@ -1756,11 +1840,14 @@
       <c r="G9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I9" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>31</v>
@@ -1778,9 +1865,12 @@
       <c r="G10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="H10" s="15"/>
+      <c r="I10" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>36</v>
@@ -1797,11 +1887,14 @@
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="H11" s="15"/>
+      <c r="I11" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
@@ -1821,9 +1914,12 @@
       <c r="F16" s="4"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="13.5" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="I16" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
+    <row r="19" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>43</v>
       </c>
@@ -1845,8 +1941,11 @@
         <v>46</v>
       </c>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.15">
+      <c r="I19" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>22</v>
@@ -1868,8 +1967,11 @@
       <c r="H20" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I20" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>51</v>
@@ -1887,8 +1989,11 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I21" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>54</v>
       </c>
@@ -1910,8 +2015,11 @@
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I24" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>58</v>
@@ -1933,8 +2041,11 @@
         <v>61</v>
       </c>
       <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I25" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>51</v>
@@ -1951,8 +2062,11 @@
         <v>64</v>
       </c>
       <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I26" s="16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>65</v>
@@ -1965,8 +2079,11 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I27" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>67</v>
@@ -1981,8 +2098,11 @@
         <v>69</v>
       </c>
       <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I28" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>70</v>
@@ -1995,8 +2115,11 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I29" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>72</v>
@@ -2012,8 +2135,11 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I30" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
@@ -2029,8 +2155,11 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-    </row>
-    <row r="33" spans="1:8" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="I31" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>76</v>
       </c>
@@ -2050,8 +2179,11 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I33" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>58</v>
@@ -2066,8 +2198,11 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="I34" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>51</v>
@@ -2085,8 +2220,11 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-    </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I35" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>82</v>
       </c>
@@ -2103,8 +2241,11 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I38" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
@@ -2115,8 +2256,11 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I39" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
@@ -2127,8 +2271,11 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-    </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I40" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="12" t="s">
         <v>122</v>
       </c>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141A2220-11EA-4F63-980D-9BA014410543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F555F09-B65E-4820-B4E8-E6BD41C143D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel分镜" sheetId="1" r:id="rId1"/>
@@ -502,9 +502,6 @@
 </t>
   </si>
   <si>
-    <t>笔记本铃声，AI逐渐靠近的脚步声</t>
-  </si>
-  <si>
     <t>3. 夜晚，熄灯的公司房间内</t>
   </si>
   <si>
@@ -515,9 +512,6 @@
     <t>0：08 音乐淡出，玩家杀死AI，玩家拾取地上钥匙卡</t>
   </si>
   <si>
-    <t>笔记本铃声，轻微的敌人倒地声，卡片掉落声</t>
-  </si>
-  <si>
     <t>笔记本亮屏画面，笔记本铃声</t>
   </si>
   <si>
@@ -531,9 +525,6 @@
   </si>
   <si>
     <t>3s左右，无BGM</t>
-  </si>
-  <si>
-    <t>玩家拾取声音</t>
   </si>
   <si>
     <t>敌人死后钥匙卡生成</t>
@@ -959,6 +950,18 @@
   </si>
   <si>
     <t>LOGO出现，音乐停止</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>笔记本铃声，AI逐渐靠近的脚步声</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>笔记本铃声，轻微的敌人倒地声，卡片掉落声</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家拾取声音</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1113,17 +1116,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1685,13 +1688,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -1717,11 +1720,11 @@
       <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="16" t="s">
-        <v>127</v>
+      <c r="I3" s="14" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1741,18 +1744,18 @@
         <f ca="1">_xlfn.DISPIMG("ID_B84541FE2FE54F2DB9CCA8A7E12DD669",1)</f>
         <v>#NAME?</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="16" t="s">
-        <v>128</v>
+      <c r="I5" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1762,14 +1765,14 @@
         <v>16</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="13"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="16" t="s">
-        <v>128</v>
+      <c r="I6" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1779,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="16" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1788,11 +1791,11 @@
       <c r="G7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="16" t="s">
-        <v>129</v>
+      <c r="I7" s="14" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.15">
@@ -1807,142 +1810,142 @@
         <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
         <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="3" t="s">
-        <v>24</v>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="16" t="s">
-        <v>130</v>
+      <c r="I8" s="14" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</f>
         <v>=DISPIMG("ID_BB7F924D1CEF4F73969797648F9C0D95",1)</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="H9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>131</v>
+      <c r="I9" s="14" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="16" t="s">
-        <v>128</v>
+        <v>32</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</f>
         <v>=DISPIMG("ID_2727A45A097247A0879B7366244099D9",1)</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16" t="s">
-        <v>132</v>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="13" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D16" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</f>
         <v>=DISPIMG("ID_EE9B9E45B4774B70A5B8B67C810CE05C",1)</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="16" t="s">
-        <v>133</v>
+      <c r="I16" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
     <row r="19" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="16" t="s">
-        <v>133</v>
+      <c r="I19" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1951,333 +1954,333 @@
         <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</f>
         <v>=DISPIMG("ID_0948A93434EC49A8B2270DD0488BD38C",1)</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>133</v>
+        <v>47</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</f>
         <v>=DISPIMG("ID_416C068A1BF74DB8AA3BF66DC3DC2453",1)</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="16" t="s">
-        <v>134</v>
+      <c r="I21" s="14" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</f>
         <v>=DISPIMG("ID_C1248B16276447BFAED54F0BBE5CA2D7",1)</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="16" t="s">
-        <v>128</v>
+      <c r="I24" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D25" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</f>
         <v>=DISPIMG("ID_13F9596BDB8E47DA83C2BF5AEF5E6670",1)</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="16" t="s">
-        <v>128</v>
+      <c r="I25" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="14" t="s">
-        <v>63</v>
+      <c r="E26" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="16" t="s">
-        <v>135</v>
+      <c r="I26" s="14" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="14"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="16" t="s">
-        <v>133</v>
+      <c r="I27" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="14"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="16" t="s">
-        <v>133</v>
+      <c r="I28" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="14"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="16" t="s">
-        <v>133</v>
+      <c r="I29" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D30" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
         <v>=DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="16" t="s">
-        <v>133</v>
+      <c r="I30" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D31" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="16" t="s">
-        <v>136</v>
+      <c r="I31" s="14" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D33" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="16" t="s">
-        <v>128</v>
+      <c r="I33" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="16" t="s">
-        <v>137</v>
+      <c r="I34" s="14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D35" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="16" t="s">
-        <v>133</v>
+      <c r="I35" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="16" t="s">
         <v>82</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="14" t="s">
-        <v>85</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="16" t="s">
-        <v>133</v>
+      <c r="I38" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="13"/>
+      <c r="E39" s="15"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="16" t="s">
-        <v>133</v>
+      <c r="I39" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="16" t="s">
-        <v>138</v>
+      <c r="I40" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2306,132 +2309,132 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="9"/>
       <c r="B3" s="8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="9"/>
       <c r="B4" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="9"/>
       <c r="B5" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="9"/>
       <c r="B6" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="9"/>
       <c r="B7" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="9"/>
       <c r="B8" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="9"/>
       <c r="B9" s="8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="9"/>
       <c r="B10" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -2452,7 +2455,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="F13" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -2461,7 +2464,7 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="F14" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -2520,12 +2523,12 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="F32" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.15">
       <c r="F51" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F555F09-B65E-4820-B4E8-E6BD41C143D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36A79B7-6340-4D4C-8297-1CA099E4EF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel分镜" sheetId="1" r:id="rId1"/>
@@ -1806,9 +1806,9 @@
       <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="3" t="str">
-        <f>_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
-        <v>=DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</v>
+      <c r="D8" s="3" t="e">
+        <f ca="1">_xlfn.DISPIMG("ID_4268D545E68F45B69E2BA538EB8278BE",1)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="14" t="s">

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36A79B7-6340-4D4C-8297-1CA099E4EF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83122E30-B944-460B-9C58-8FDC2241DD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="140">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -609,9 +609,6 @@
     <t>Abel的配音</t>
   </si>
   <si>
-    <t>玩家使用扫描，探查出楼内的AI</t>
-  </si>
-  <si>
     <t>1：14 - 1：31(They wanna stop us)
 玩家进入骇客模式并且使用扫描的瞬间，BGM立刻开始
 玩家放置完重生点后，BGM淡出</t>
@@ -644,22 +641,10 @@
     <t>7. 夜晚，明亮的大厅内</t>
   </si>
   <si>
-    <t>玩家打碎门口摄像头，玩家在一个门口放置重生点</t>
-  </si>
-  <si>
-    <t>玩家开门，进入房间，被四面八方的敌人射死</t>
-  </si>
-  <si>
     <t>5s左右，无BGM</t>
   </si>
   <si>
     <t>章节五</t>
-  </si>
-  <si>
-    <t>玩家在门口重生点重生，看到门口的售货机，购买神秘武器。</t>
-  </si>
-  <si>
-    <t>玩家走向门，随着离门越来越近，BGM声音越来越大</t>
   </si>
   <si>
     <t>1：50 - 1：54 音乐淡入</t>
@@ -962,6 +947,30 @@
   </si>
   <si>
     <t>玩家拾取声音</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. 夜晚，明亮的大厅内</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家打碎门口摄像头</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家在电梯门口放置重生点，电梯到达底层，被四面八方的敌人射死（5s左右，无BGM）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家使用扫描，探查出楼内的AI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家在电梯门口重生点重生，看到门口的售货机，购买神秘武器。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家乘着电梯下行，随着离底部es越来越近，BGM声音越来越大</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1031,7 +1040,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1067,6 +1076,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1076,7 +1122,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1126,6 +1172,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1688,13 +1743,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -1724,7 +1779,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1755,7 +1810,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1772,7 +1827,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1795,7 +1850,7 @@
         <v>21</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.15">
@@ -1812,14 +1867,14 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="14" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1838,7 +1893,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>27</v>
@@ -1847,7 +1902,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1863,14 +1918,14 @@
         <v>31</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1892,7 +1947,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="13"/>
       <c r="I11" s="14" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -1918,7 +1973,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -1945,7 +2000,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1971,7 +2026,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1993,7 +2048,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="14" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -2019,7 +2074,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -2045,7 +2100,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -2053,137 +2108,142 @@
       <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="16" t="s">
-        <v>60</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="14" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="16"/>
+      <c r="E27" s="18"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="16"/>
+      <c r="E28" s="18"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="16"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="D30" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
         <v>=DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</v>
       </c>
-      <c r="E30" s="16"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3" t="s">
-        <v>71</v>
+      <c r="B31" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
         <v>=DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>72</v>
-      </c>
+      <c r="E31" s="19"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="14" t="s">
-        <v>133</v>
-      </c>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>74</v>
+      <c r="C33" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="D33" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2191,18 +2251,18 @@
       <c r="B34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>75</v>
+      <c r="C34" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="14" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
@@ -2211,48 +2271,48 @@
         <v>48</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D35" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="15"/>
@@ -2260,14 +2320,14 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2275,20 +2335,20 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E26:E30"/>
     <mergeCell ref="E38:E39"/>
+    <mergeCell ref="E26:E31"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2309,132 +2369,132 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="9"/>
       <c r="B3" s="8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="9"/>
       <c r="B4" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="9"/>
       <c r="B5" s="8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="9"/>
       <c r="B6" s="8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="9"/>
       <c r="B7" s="8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="9"/>
       <c r="B8" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="9"/>
       <c r="B9" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="9"/>
       <c r="B10" s="8" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -2455,7 +2515,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="F13" s="11" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -2464,7 +2524,7 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="F14" s="7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -2523,12 +2583,12 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="F32" s="7" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.15">
       <c r="F51" s="7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83122E30-B944-460B-9C58-8FDC2241DD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DA3365-702C-47C2-92E3-E71BC2457DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="147">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -624,9 +624,6 @@
   </si>
   <si>
     <t>5. 夜晚，明亮的大厅内</t>
-  </si>
-  <si>
-    <t>玩家对天花板去物质化，天花板上面的物体掉下来砸死AI</t>
   </si>
   <si>
     <t>掉落发出响声和掉落杀死AI的物体Mesh</t>
@@ -971,6 +968,38 @@
   </si>
   <si>
     <t>玩家乘着电梯下行，随着离底部es越来越近，BGM声音越来越大</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家对地板去物质化，AI坠落死亡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T4-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T4-4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T4-6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T4-7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T4-8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T5-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T5-2~5-3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1743,13 +1772,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="E1" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -1779,7 +1808,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1810,7 +1839,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1827,7 +1856,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1850,7 +1879,7 @@
         <v>21</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.15">
@@ -1867,14 +1896,14 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1893,7 +1922,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>27</v>
@@ -1902,7 +1931,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -1918,14 +1947,14 @@
         <v>31</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1947,7 +1976,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="13"/>
       <c r="I11" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -1973,7 +2002,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13.5" x14ac:dyDescent="0.15"/>
@@ -2000,7 +2029,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2026,7 +2055,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -2048,7 +2077,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -2074,7 +2103,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
@@ -2100,7 +2129,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -2109,7 +2138,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="17" t="s">
@@ -2121,7 +2150,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -2136,9 +2165,11 @@
       <c r="E27" s="18"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="14" t="s">
+        <v>141</v>
+      </c>
       <c r="I27" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -2146,44 +2177,48 @@
       <c r="B28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>64</v>
+      <c r="C28" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="18"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>140</v>
+      </c>
       <c r="I28" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="18"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
+      <c r="H29" s="14" t="s">
+        <v>142</v>
+      </c>
       <c r="I29" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D30" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_41F1A86A32A24A11B6376CA514625CA0",1)</f>
@@ -2192,18 +2227,20 @@
       <c r="E30" s="18"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="H30" s="14" t="s">
+        <v>143</v>
+      </c>
       <c r="I30" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="B31" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_90B36DA5FDC14F3381253880B535F5A5",1)</f>
@@ -2212,9 +2249,11 @@
       <c r="E31" s="19"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="I31" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -2224,26 +2263,28 @@
     </row>
     <row r="33" spans="1:9" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D33" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</f>
         <v>=DISPIMG("ID_3737BFE793EF4D8C8AB94AF3F72694BC",1)</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="14" t="s">
+        <v>145</v>
+      </c>
       <c r="I33" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2252,17 +2293,19 @@
         <v>55</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="H34" s="14" t="s">
+        <v>146</v>
+      </c>
       <c r="I34" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
@@ -2271,48 +2314,50 @@
         <v>48</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="3" t="str">
         <f>_xlfn.DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</f>
         <v>=DISPIMG("ID_548AC508B2354AD98DEE784314410537",1)</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+      <c r="H35" s="14" t="s">
+        <v>146</v>
+      </c>
       <c r="I35" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="15"/>
@@ -2320,14 +2365,14 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2335,12 +2380,12 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2369,132 +2414,132 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="9"/>
       <c r="B3" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="9"/>
       <c r="B4" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="9"/>
       <c r="B5" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="9"/>
       <c r="B6" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="9"/>
       <c r="B7" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="9"/>
       <c r="B8" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="9"/>
       <c r="B9" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="9"/>
       <c r="B10" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -2515,7 +2560,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="F13" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -2524,7 +2569,7 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="F14" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -2583,12 +2628,12 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="F32" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.15">
       <c r="F51" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/GD12Trailer/3DFinal_Trailer分镜.xlsx
+++ b/GD12Trailer/3DFinal_Trailer分镜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\GD12_3DFinal\GD12Trailer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DA3365-702C-47C2-92E3-E71BC2457DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C716277-AF17-4CAE-BC14-9651E97A03C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30570" yWindow="3000" windowWidth="26190" windowHeight="11430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel分镜" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="151">
   <si>
     <t>大体剧情流</t>
   </si>
@@ -1000,6 +1000,22 @@
   </si>
   <si>
     <t>完成：T5-2~5-3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T3-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T3-3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒放T3-3和T3-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成：T4-2~4-3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2027,7 +2043,9 @@
       <c r="G19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="14" t="s">
+        <v>147</v>
+      </c>
       <c r="I19" s="14" t="s">
         <v>124</v>
       </c>
@@ -2075,7 +2093,9 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="I21" s="14" t="s">
         <v>125</v>
       </c>
@@ -2101,7 +2121,9 @@
         <v>54</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="14" t="s">
+        <v>149</v>
+      </c>
       <c r="I24" s="14" t="s">
         <v>119</v>
       </c>
@@ -2127,7 +2149,9 @@
       <c r="G25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="3"/>
+      <c r="H25" s="14" t="s">
+        <v>150</v>
+      </c>
       <c r="I25" s="14" t="s">
         <v>119</v>
       </c>
@@ -2148,7 +2172,9 @@
       <c r="G26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="3"/>
+      <c r="H26" s="14" t="s">
+        <v>150</v>
+      </c>
       <c r="I26" s="14" t="s">
         <v>126</v>
       </c>
